--- a/data/trans_bre/IP24_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP24_R-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 14,84</t>
+          <t>-5,55; 14,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 14,25</t>
+          <t>-3,85; 13,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,34; 22,23</t>
+          <t>0,51; 22,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,26; 31,25</t>
+          <t>-8,3; 32,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-23,66; 100,34</t>
+          <t>-22,7; 92,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-21,95; 177,03</t>
+          <t>-27,63; 156,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 338,18</t>
+          <t>-0,82; 327,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-35,88; 214,75</t>
+          <t>-35,76; 217,43</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 8,11</t>
+          <t>-1,19; 7,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,41; 9,54</t>
+          <t>1,16; 9,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,1; 11,05</t>
+          <t>2,85; 11,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,47; 22,28</t>
+          <t>-0,55; 20,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 39,55</t>
+          <t>-5,03; 38,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,37; 67,08</t>
+          <t>6,89; 69,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,85; 84,85</t>
+          <t>16,15; 91,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 133,42</t>
+          <t>-6,28; 121,17</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,48; 4,44</t>
+          <t>-11,35; 3,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 8,45</t>
+          <t>-6,14; 7,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,19; 5,27</t>
+          <t>-9,37; 5,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 8,1</t>
+          <t>-6,02; 8,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-36,72; 20,64</t>
+          <t>-35,41; 18,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-28,47; 62,06</t>
+          <t>-29,44; 58,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-32,4; 24,51</t>
+          <t>-32,64; 24,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-29,02; 63,79</t>
+          <t>-32,0; 61,79</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 5,9</t>
+          <t>-1,6; 5,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,88; 7,72</t>
+          <t>0,83; 7,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,6; 8,27</t>
+          <t>1,64; 8,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 16,07</t>
+          <t>0,03; 16,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-7,44; 27,77</t>
+          <t>-6,24; 25,74</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,63; 54,79</t>
+          <t>4,33; 51,58</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,06; 54,03</t>
+          <t>9,02; 58,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 95,47</t>
+          <t>-0,8; 98,47</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP24_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP24_R-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 14,2</t>
+          <t>-5,77; 13,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 13,25</t>
+          <t>-3,77; 14,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,51; 22,67</t>
+          <t>-0,44; 22,24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,3; 32,35</t>
+          <t>-8,84; 30,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-22,7; 92,54</t>
+          <t>-23,09; 96,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-27,63; 156,95</t>
+          <t>-22,38; 183,45</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 327,62</t>
+          <t>-11,75; 316,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-35,76; 217,43</t>
+          <t>-35,57; 206,95</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 7,93</t>
+          <t>-1,22; 7,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,16; 9,94</t>
+          <t>0,96; 9,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,85; 11,5</t>
+          <t>3,31; 11,56</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 20,75</t>
+          <t>-0,64; 20,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 38,95</t>
+          <t>-5,33; 38,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,89; 69,86</t>
+          <t>5,12; 68,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,15; 91,0</t>
+          <t>19,9; 94,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 121,17</t>
+          <t>-5,82; 126,51</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,35; 3,98</t>
+          <t>-10,44; 4,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 7,67</t>
+          <t>-5,91; 8,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,37; 5,12</t>
+          <t>-9,22; 5,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 8,24</t>
+          <t>-5,62; 8,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-35,41; 18,25</t>
+          <t>-33,57; 18,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-29,44; 58,17</t>
+          <t>-28,93; 64,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-32,64; 24,32</t>
+          <t>-33,26; 26,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-32,0; 61,79</t>
+          <t>-28,39; 69,98</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 5,52</t>
+          <t>-1,84; 5,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,83; 7,6</t>
+          <t>0,89; 7,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,64; 8,55</t>
+          <t>1,71; 8,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,03; 16,9</t>
+          <t>-0,21; 16,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 25,74</t>
+          <t>-7,24; 25,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,33; 51,58</t>
+          <t>5,1; 51,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,02; 58,78</t>
+          <t>8,73; 53,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 98,47</t>
+          <t>-2,2; 95,73</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP24_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP24_R-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,08</t>
+          <t>-1,22</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>-5,91%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 13,6</t>
+          <t>-5,71; 14,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 14,37</t>
+          <t>-3,29; 14,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 22,24</t>
+          <t>0,34; 22,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,84; 30,96</t>
+          <t>-13,51; 11,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-23,09; 96,06</t>
+          <t>-23,66; 100,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-22,38; 183,45</t>
+          <t>-21,95; 177,03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-11,75; 316,89</t>
+          <t>-2,62; 338,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-35,57; 206,95</t>
+          <t>-51,4; 85,39</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6,73</t>
+          <t>1,96</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>11,88%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 7,97</t>
+          <t>-1,22; 8,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,96; 9,85</t>
+          <t>1,41; 9,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,31; 11,56</t>
+          <t>3,1; 11,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 20,37</t>
+          <t>-3,7; 6,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 38,7</t>
+          <t>-4,9; 39,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,12; 68,82</t>
+          <t>7,37; 67,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,9; 94,67</t>
+          <t>17,85; 84,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 126,51</t>
+          <t>-19,46; 46,67</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,96</t>
+          <t>0,42</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,44; 4,35</t>
+          <t>-11,48; 4,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 8,22</t>
+          <t>-5,7; 8,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,22; 5,46</t>
+          <t>-9,19; 5,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 8,54</t>
+          <t>-5,94; 7,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-33,57; 18,96</t>
+          <t>-36,72; 20,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-28,93; 64,22</t>
+          <t>-28,47; 62,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-33,26; 26,95</t>
+          <t>-32,4; 24,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-28,39; 69,98</t>
+          <t>-31,82; 62,54</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,58</t>
+          <t>1,33</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 5,51</t>
+          <t>-1,87; 5,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,89; 7,54</t>
+          <t>0,88; 7,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,71; 8,43</t>
+          <t>1,6; 8,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 16,26</t>
+          <t>-2,88; 5,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-7,24; 25,16</t>
+          <t>-7,44; 27,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,1; 51,82</t>
+          <t>4,63; 54,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,73; 53,99</t>
+          <t>9,06; 54,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 95,73</t>
+          <t>-16,33; 35,76</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP24_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP24_R-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>4,48</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>4,88</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>10,79</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-1,22</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>22,33%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>39,41%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>97,27%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-5,91%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>4.475412684909361</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>4.883090920111627</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>10.79208463730559</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-1.217704560167357</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.2232594453063351</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.394078131161448</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.9726714982293466</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.05912703805717661</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-5,71; 14,84</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-3,29; 14,25</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,34; 22,23</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-13,51; 11,82</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-23,66; 100,34</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-21,95; 177,03</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-2,62; 338,18</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-51,4; 85,39</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-5.709617839580257</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-3.288470417823258</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.3407699606154311</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-13.51193905133227</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.2366315199001185</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.2194516565044683</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.0262161256895408</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.5140185311255476</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>14.84480204434792</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>14.25289977470547</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>22.23426519363102</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>11.82090888334614</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>1.003415392044808</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>1.77033653590337</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>3.381805471131735</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.8539156165675923</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>3,51</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>5,57</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>7,11</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1,96</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>15,53%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>34,31%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>48,54%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>11,88%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-1,22; 8,11</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>1,41; 9,54</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>3,1; 11,05</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-3,7; 6,72</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-4,9; 39,55</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>7,37; 67,08</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>17,85; 84,85</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-19,46; 46,67</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>3.50629335631267</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>5.567794682232916</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>7.114982943374478</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>1.957852216931899</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.1553301693113809</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.3431240278199193</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.4853895902403343</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.1187751297445046</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-3,63</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1,11</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,99</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,42</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-13,23%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>6,58%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-8,11%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2,74%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-1.215295965310832</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>1.407770956565592</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>3.104290882833083</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-3.700350558987727</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.04896557812848485</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>0.07369596936525354</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>0.1784907957358606</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.1946457638623602</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-11,48; 4,44</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-5,7; 8,45</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-9,19; 5,27</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-5,94; 7,54</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-36,72; 20,64</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-28,47; 62,06</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-32,4; 24,51</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-31,82; 62,54</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>8.113001080537991</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>9.542895306685466</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>11.05236533243948</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>6.724136734963242</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.3955388076774984</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.6707697279293806</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.8484870577809168</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.4667035319414476</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,97 +819,197 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>1,96</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>4,37</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>5,16</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,33</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>8,4%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>27,39%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>30,71%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>8,06%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-3.631774419090492</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>1.114788587693011</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-1.985762848899944</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0.4205573701960313</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.1323232304475975</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.06582496249936229</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.08114788930941835</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.02737167456268993</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-1,87; 5,9</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>0,88; 7,72</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1,6; 8,27</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-2,88; 5,18</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-7,44; 27,77</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>4,63; 54,79</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>9,06; 54,03</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-16,33; 35,76</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-11.48349973447998</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-5.695451450830335</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-9.18658546334585</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-5.935249234202876</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.3671981448142704</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.2847157629754358</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.3239932890050431</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.3182387459986423</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>4.444306683348241</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>8.449936696432061</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>5.271656096751222</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>7.536891075407739</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.2063700112155295</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.6206051296224749</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.2451485146298379</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.62538520475215</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>1.960495092933207</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>4.370046185999513</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>5.158983543142718</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>1.332692604273494</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.08402037827517518</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.2738762232442147</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.3071041157382747</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.08055805782005042</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-1.869408103173402</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.8759124357504424</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>1.600244214485234</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-2.880447122985881</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.07435155413082897</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>0.04625095061653831</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>0.09056376903349926</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.163317247363436</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>5.898150197524586</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>7.72190313730147</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>8.271142472386536</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>5.183371375324285</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.2776543452926917</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.5479343110560633</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.5402743767416384</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.3576417844615773</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1008,13 +1017,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
